--- a/Tabla2_CarAccidentsData.xlsx
+++ b/Tabla2_CarAccidentsData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msamper\Dropbox\LIBRO\Repositorio de datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CAMILA SAMPER\Dropbox\LIBRO\Repositorio de datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C5E50FE6-32B9-409A-A779-041DC4D7A15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724CC1C7-42FF-42A0-A4FB-58385CED446F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2DF06FF3-52B9-499B-B0D2-C28FAD31714D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2DF06FF3-52B9-499B-B0D2-C28FAD31714D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla 2_Datos accidente tránsit" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,6 @@
     <t>Hombre</t>
   </si>
   <si>
-    <t>01/15/2025</t>
-  </si>
-  <si>
     <t>Bogotá D.C.</t>
   </si>
   <si>
@@ -91,9 +88,6 @@
     <t>Femenino</t>
   </si>
   <si>
-    <t>2025-13-01</t>
-  </si>
-  <si>
     <t>Barranquilla</t>
   </si>
   <si>
@@ -157,9 +151,6 @@
     <t>Villavo</t>
   </si>
   <si>
-    <t>31/02/2025</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -182,6 +173,15 @@
   </si>
   <si>
     <t xml:space="preserve">Medellín </t>
+  </si>
+  <si>
+    <t>01/15/2026</t>
+  </si>
+  <si>
+    <t>2026-22-01</t>
+  </si>
+  <si>
+    <t>31/02/2026</t>
   </si>
 </sst>
 </file>
@@ -548,7 +548,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -711,6 +711,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -756,7 +771,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -767,51 +782,24 @@
     <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="34" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="20" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="19" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="36" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -821,7 +809,37 @@
     <xf numFmtId="0" fontId="19" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="19" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="36" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1200,16 +1218,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A08E36C-4A08-44EC-B70C-8187CCD1F91E}">
   <dimension ref="A1:E41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1226,676 +1244,676 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
-        <v>45669</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="B2" s="13">
+        <v>46016</v>
+      </c>
+      <c r="C2" s="4">
         <v>34</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
-        <v>45670</v>
-      </c>
-      <c r="C3" s="8">
+      <c r="B3" s="14">
+        <v>46018</v>
+      </c>
+      <c r="C3" s="6">
         <v>27</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>45671</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" s="15">
+        <v>46036</v>
+      </c>
+      <c r="C4" s="4">
         <v>-5</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="6">
+        <v>45</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="8">
-        <v>45</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
-        <v>45673</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="B6" s="15">
+        <v>46038</v>
+      </c>
+      <c r="C6" s="4">
         <v>130</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17">
+        <v>45674</v>
+      </c>
+      <c r="C7" s="8">
+        <v>29</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11">
-        <v>45674</v>
-      </c>
-      <c r="C7" s="12">
-        <v>29</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
-        <v>45675</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B8" s="15">
+        <v>46040</v>
+      </c>
+      <c r="C8" s="4">
         <v>18</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="5" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14">
+        <v>46041</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7">
-        <v>45676</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
-        <v>45677</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="B10" s="15">
+        <v>46042</v>
+      </c>
+      <c r="C10" s="4">
         <v>22</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14">
+        <v>46043</v>
+      </c>
+      <c r="C11" s="6">
+        <v>31</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7">
-        <v>45678</v>
-      </c>
-      <c r="C11" s="8">
-        <v>31</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="4">
+        <v>41</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>12</v>
+      </c>
+      <c r="B13" s="19">
+        <v>46045</v>
+      </c>
+      <c r="C13" s="8">
+        <v>55</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="5">
-        <v>41</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
-        <v>12</v>
-      </c>
-      <c r="B13" s="14">
-        <v>45680</v>
-      </c>
-      <c r="C13" s="12">
-        <v>55</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E13" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="4">
-        <v>45683</v>
-      </c>
-      <c r="C14" s="5">
+      <c r="B14" s="15">
+        <v>46048</v>
+      </c>
+      <c r="C14" s="4">
         <v>38</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="14">
+        <v>46049</v>
+      </c>
+      <c r="C15" s="6">
+        <v>34</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6">
-        <v>14</v>
-      </c>
-      <c r="B15" s="7">
-        <v>45684</v>
-      </c>
-      <c r="C15" s="8">
-        <v>34</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="4">
-        <v>45685</v>
-      </c>
-      <c r="C16" s="5">
+      <c r="B16" s="15">
+        <v>46050</v>
+      </c>
+      <c r="C16" s="4">
         <v>19</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6">
+      <c r="D16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="11">
-        <v>45686</v>
-      </c>
-      <c r="C17" s="12">
+      <c r="B17" s="17">
+        <v>46051</v>
+      </c>
+      <c r="C17" s="8">
         <v>20</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="12" t="s">
+      <c r="D17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="4">
-        <v>45687</v>
-      </c>
-      <c r="C18" s="5">
+      <c r="B18" s="15">
+        <v>46052</v>
+      </c>
+      <c r="C18" s="4">
         <v>21</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="7">
+        <v>18</v>
+      </c>
+      <c r="B19" s="14">
+        <v>46053</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
-        <v>18</v>
-      </c>
-      <c r="B19" s="7">
-        <v>45688</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="4">
-        <v>45689</v>
-      </c>
-      <c r="C20" s="5">
+      <c r="B20" s="15">
+        <v>46054</v>
+      </c>
+      <c r="C20" s="4">
         <v>42</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6">
+      <c r="D20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="7">
-        <v>45690</v>
-      </c>
-      <c r="C21" s="8">
+      <c r="B21" s="14">
+        <v>46055</v>
+      </c>
+      <c r="C21" s="6">
         <v>39</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="8" t="s">
+      <c r="D21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="4">
-        <v>45691</v>
-      </c>
-      <c r="C22" s="5">
+      <c r="B22" s="15">
+        <v>46056</v>
+      </c>
+      <c r="C22" s="4">
         <v>-12</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="5">
+        <v>22</v>
+      </c>
+      <c r="B23" s="19">
+        <v>46057</v>
+      </c>
+      <c r="C23" s="8">
+        <v>25</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="6">
-        <v>22</v>
-      </c>
-      <c r="B23" s="14">
-        <v>45692</v>
-      </c>
-      <c r="C23" s="12">
-        <v>25</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="4">
-        <v>45695</v>
-      </c>
-      <c r="C24" s="5">
+      <c r="B24" s="15">
+        <v>46060</v>
+      </c>
+      <c r="C24" s="4">
         <v>71</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="5" t="s">
+      <c r="D24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
+    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="7">
         <v>24</v>
       </c>
-      <c r="B25" s="7">
-        <v>45696</v>
-      </c>
-      <c r="C25" s="8">
+      <c r="B25" s="14">
+        <v>46061</v>
+      </c>
+      <c r="C25" s="6">
         <v>69</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="4">
-        <v>45697</v>
-      </c>
-      <c r="C26" s="5">
+      <c r="B26" s="15">
+        <v>46062</v>
+      </c>
+      <c r="C26" s="4">
         <v>150</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="5" t="s">
+      <c r="D26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6">
+    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="14">
-        <v>45698</v>
-      </c>
-      <c r="C27" s="12">
+      <c r="B27" s="19">
+        <v>46063</v>
+      </c>
+      <c r="C27" s="8">
         <v>48</v>
       </c>
-      <c r="D27" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="12" t="s">
+      <c r="D27" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="4">
-        <v>45699</v>
-      </c>
-      <c r="C28" s="5">
+      <c r="B28" s="15">
+        <v>46064</v>
+      </c>
+      <c r="C28" s="4">
         <v>49</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="5">
+        <v>28</v>
+      </c>
+      <c r="B29" s="14">
+        <v>46065</v>
+      </c>
+      <c r="C29" s="6">
+        <v>17</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6">
-        <v>28</v>
-      </c>
-      <c r="B29" s="7">
-        <v>45700</v>
-      </c>
-      <c r="C29" s="8">
-        <v>17</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E29" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="4">
-        <v>45701</v>
-      </c>
-      <c r="C30" s="5">
+      <c r="B30" s="15">
+        <v>46066</v>
+      </c>
+      <c r="C30" s="4">
         <v>8.1</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="10">
+      <c r="D30" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="7">
         <v>30</v>
       </c>
-      <c r="B31" s="7">
-        <v>45702</v>
-      </c>
-      <c r="C31" s="8">
+      <c r="B31" s="14">
+        <v>46067</v>
+      </c>
+      <c r="C31" s="6">
         <v>19</v>
       </c>
-      <c r="D31" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" s="8" t="s">
+      <c r="D31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="16">
+      <c r="B32" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="9">
         <v>28</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6">
+      <c r="E32" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="5">
         <v>32</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="12">
+      <c r="B33" s="21"/>
+      <c r="C33" s="8">
         <v>44</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E33" s="12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E33" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="18">
-        <v>45708</v>
-      </c>
-      <c r="C34" s="16">
+      <c r="B34" s="22">
+        <v>46101</v>
+      </c>
+      <c r="C34" s="9">
         <v>35</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="16" t="s">
+      <c r="D34" s="10"/>
+      <c r="E34" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="6">
+    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" s="14">
-        <v>45709</v>
-      </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="19">
+        <v>46102</v>
+      </c>
+      <c r="C35" s="11"/>
+      <c r="D35" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="18">
-        <v>45710</v>
-      </c>
-      <c r="C36" s="16">
+      <c r="B36" s="22">
+        <v>46103</v>
+      </c>
+      <c r="C36" s="9">
         <v>40</v>
       </c>
-      <c r="D36" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" s="19"/>
-    </row>
-    <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="10">
+      <c r="D36" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="10"/>
+    </row>
+    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="7">
         <v>36</v>
       </c>
-      <c r="B37" s="14">
-        <v>45711</v>
-      </c>
-      <c r="C37" s="12">
+      <c r="B37" s="19">
+        <v>46120</v>
+      </c>
+      <c r="C37" s="8">
         <v>36</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="12">
+        <v>37</v>
+      </c>
+      <c r="B38" s="22">
+        <v>46136</v>
+      </c>
+      <c r="C38" s="9">
+        <v>37</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="5">
+        <v>38</v>
+      </c>
+      <c r="B39" s="23">
+        <v>46198</v>
+      </c>
+      <c r="C39" s="8">
+        <v>38</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="21">
-        <v>37</v>
-      </c>
-      <c r="B38" s="18">
-        <v>45712</v>
-      </c>
-      <c r="C38" s="16">
-        <v>37</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="6">
-        <v>38</v>
-      </c>
-      <c r="B39" s="22">
-        <v>45713</v>
-      </c>
-      <c r="C39" s="12">
-        <v>38</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" s="18">
-        <v>45714</v>
-      </c>
-      <c r="C40" s="16">
+      <c r="B40" s="22">
+        <v>46199</v>
+      </c>
+      <c r="C40" s="9">
         <v>39</v>
       </c>
-      <c r="D40" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E40" s="16" t="s">
+      <c r="D40" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6">
+    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="14">
-        <v>45715</v>
-      </c>
-      <c r="C41" s="12">
+      <c r="B41" s="19">
+        <v>46200</v>
+      </c>
+      <c r="C41" s="8">
         <v>999</v>
       </c>
-      <c r="D41" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>19</v>
+      <c r="D41" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
